--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R5f909ec1c3f4462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb4bea453b7f04545"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,7 +346,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>脱敏客服工单、批量动作规则、虚拟列表页面与业务场景</x:v>
+        <x:v>本次客服工单队列发布批次，包括字段已脱敏的工单、批量动作规则、虚拟列表页面与业务场景</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
@@ -413,28 +413,20 @@
         <x:v>expected_result为undone时按audit_clock推进时间并点击Undo assignment，恢复输入中的工单状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="33" customHeight="1">
+    <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>报告交付</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>npm run process正常结束，配置、测试和三份报告可读且能按业务主键回查输入与DOM</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="33" customHeight="1">
+        <x:v>选择矩阵记录场景与工单结果，撤销时序记录业务时钟与恢复结果，ARIA合同记录页面角色、属性和可访问名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
       <x:c r="A15" s="5" t="str">
-        <x:v>业务核对点</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>窗口标签、ARIA属性、选中集合、route请求、动作结果、撤销时钟和输入保全</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="33" customHeight="1">
-      <x:c r="A16" s="5" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B16" s="5" t="str">
-        <x:v>函数拆分、变量名、CSV行顺序、回环端口号、测试辅助文件和等价稳定定位器</x:v>
+        <x:v>输入页面、工单、规则和场景保持只读，业务运行只访问本机页面，配置、用例和三份报告只写入output目录</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb4bea453b7f04545"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R7c08d405231342ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -351,23 +351,23 @@
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务输入</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>解压输入数据包后，在input_data读取app、fixtures、starter、scripts和tools</x:v>
+        <x:v>app目录；fixtures/tickets.json；fixtures/bulk_rules.json；fixtures/selection_cases.csv；starter目录</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>发布目标</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>app目录；fixtures/tickets.json；fixtures/bulk_rules.json；fixtures/selection_cases.csv；starter目录</x:v>
+        <x:v>核对虚拟列表跨窗口选择、禁用工单保护、批量请求、撤销恢复和可访问属性，为发布负责人提供浏览器回归结果</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>output/playwright.config.ts；output/tests/ticket_queue_virtual_list.spec.ts；output/reports下三份CSV</x:v>
@@ -375,7 +375,7 @@
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>Playwright步骤</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
         <x:v>读取工单与规则；配置Chromium；拦截本地接口；滚动定位；跨窗口选择；执行批量动作；撤销恢复；整理报告</x:v>
@@ -413,20 +413,36 @@
         <x:v>expected_result为undone时按audit_clock推进时间并点击Undo assignment，恢复输入中的工单状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="48" customHeight="1">
+    <x:row r="14" ht="33" customHeight="1">
       <x:c r="A14" s="5" t="str">
+        <x:v>材料边界</x:v>
+      </x:c>
+      <x:c r="B14" s="5" t="str">
+        <x:v>输入页面、工单、规则和场景供浏览器测试读取，配置、用例和三份报告写入output目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="33" customHeight="1">
+      <x:c r="A15" s="5" t="str">
         <x:v>报告交付</x:v>
       </x:c>
-      <x:c r="B14" s="5" t="str">
-        <x:v>选择矩阵记录场景与工单结果，撤销时序记录业务时钟与恢复结果，ARIA合同记录页面角色、属性和可访问名称</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="5" t="str">
+      <x:c r="B15" s="5" t="str">
+        <x:v>选择矩阵交给客服工具团队，撤销时序交给发布负责人，ARIA合同交给前端团队</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="5" t="str">
+        <x:v>结果对账</x:v>
+      </x:c>
+      <x:c r="B16" s="5" t="str">
+        <x:v>工单身份、选中状态、批量请求、撤销结果和可访问属性可按业务主键在输入、浏览器观察与三份报告之间核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="33" customHeight="1">
+      <x:c r="A17" s="5" t="str">
         <x:v>实现边界</x:v>
       </x:c>
-      <x:c r="B15" s="5" t="str">
-        <x:v>输入页面、工单、规则和场景保持只读，业务运行只访问本机页面，配置、用例和三份报告只写入output目录</x:v>
+      <x:c r="B17" s="5" t="str">
+        <x:v>辅助函数、回环端口和稳定定位器可以不同，浏览器行为、业务结果与报告主键保持一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
